--- a/AAII_Financials/Quarterly/SHMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SHMD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>SHMD</t>
   </si>
@@ -1005,7 +1005,7 @@
         <v>600</v>
       </c>
       <c r="H15" s="3">
-        <v>600</v>
+        <v>1700</v>
       </c>
       <c r="I15" s="3">
         <v>900</v>
@@ -1060,7 +1060,7 @@
         <v>53800</v>
       </c>
       <c r="H17" s="3">
-        <v>37300</v>
+        <v>40600</v>
       </c>
       <c r="I17" s="3">
         <v>35700</v>
@@ -1101,7 +1101,7 @@
         <v>-37800</v>
       </c>
       <c r="H18" s="3">
-        <v>-9800</v>
+        <v>-13100</v>
       </c>
       <c r="I18" s="3">
         <v>-9400</v>
@@ -1159,7 +1159,7 @@
         <v>4</v>
       </c>
       <c r="H20" s="3">
-        <v>-10700</v>
+        <v>-14000</v>
       </c>
       <c r="I20" s="3">
         <v>-10200</v>
@@ -1200,7 +1200,7 @@
         <v>-37200</v>
       </c>
       <c r="H21" s="3">
-        <v>1500</v>
+        <v>2600</v>
       </c>
       <c r="I21" s="3">
         <v>1800</v>
@@ -1651,7 +1651,7 @@
         <v>4</v>
       </c>
       <c r="H32" s="3">
-        <v>10700</v>
+        <v>14000</v>
       </c>
       <c r="I32" s="3">
         <v>10200</v>
@@ -2006,10 +2006,10 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>16300</v>
+        <v>17400</v>
       </c>
       <c r="E44" s="3">
-        <v>17500</v>
+        <v>18800</v>
       </c>
       <c r="F44" s="3">
         <v>17700</v>
@@ -2018,10 +2018,10 @@
         <v>17800</v>
       </c>
       <c r="H44" s="3">
-        <v>18100</v>
+        <v>19500</v>
       </c>
       <c r="I44" s="3">
-        <v>17300</v>
+        <v>18700</v>
       </c>
       <c r="J44" s="3">
         <v>25400</v>
@@ -2046,11 +2046,11 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1200</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F45" s="3">
         <v>4200</v>
@@ -2058,11 +2058,11 @@
       <c r="G45" s="3">
         <v>4200</v>
       </c>
-      <c r="H45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1400</v>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J45" s="3">
         <v>24300</v>
@@ -2491,10 +2491,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>29200</v>
+        <v>28800</v>
       </c>
       <c r="E57" s="3">
-        <v>31400</v>
+        <v>17300</v>
       </c>
       <c r="F57" s="3">
         <v>24800</v>
@@ -2503,10 +2503,10 @@
         <v>25000</v>
       </c>
       <c r="H57" s="3">
-        <v>28600</v>
+        <v>15400</v>
       </c>
       <c r="I57" s="3">
-        <v>27400</v>
+        <v>14800</v>
       </c>
       <c r="J57" s="3">
         <v>25800</v>
@@ -2573,10 +2573,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>25800</v>
+        <v>21300</v>
       </c>
       <c r="E59" s="3">
-        <v>27800</v>
+        <v>38400</v>
       </c>
       <c r="F59" s="3">
         <v>47900</v>
@@ -2585,10 +2585,10 @@
         <v>48300</v>
       </c>
       <c r="H59" s="3">
-        <v>31000</v>
+        <v>41200</v>
       </c>
       <c r="I59" s="3">
-        <v>29700</v>
+        <v>39500</v>
       </c>
       <c r="J59" s="3">
         <v>47100</v>
@@ -3082,7 +3082,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-184800</v>
+        <v>-181000</v>
       </c>
       <c r="E72" s="3">
         <v>-199100</v>
